--- a/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/Categoriesassets001.xlsx
+++ b/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/Categoriesassets001.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projectManager\company\zgbs3.0_tams\tams\tams-valuation-parent\tams-valuation-lossmodel\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>评级机构类型</t>
+    <t>评级类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -42,7 +42,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>评级类型</t>
+    <t>指定评级机构</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -400,13 +400,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
